--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487749_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487749_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1616</v>
+        <v>7.3256</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5495</v>
+        <v>4.8498</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6121</v>
+        <v>2.4759</v>
       </c>
       <c r="G2" t="n">
         <v>1.5472</v>
@@ -610,13 +610,13 @@
         <v>4.2687</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6483</v>
+        <v>-0.4843</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1979</v>
+        <v>-0.8976</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5496</v>
+        <v>0.4133</v>
       </c>
       <c r="V2" t="n">
         <v>2.9641</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.176</v>
+        <v>2.9574</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6314</v>
+        <v>5.3311</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.4554</v>
+        <v>-2.3737</v>
       </c>
       <c r="G3" t="n">
         <v>2.9155</v>
@@ -688,13 +688,13 @@
         <v>2.7164</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0679</v>
+        <v>-0.1506</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0751</v>
+        <v>-0.2252</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0072</v>
+        <v>0.0746</v>
       </c>
       <c r="V3" t="n">
         <v>-1.5537</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. CUESTA DE SANTOS</t>
+          <t>A. GOMEZ SERRANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7452</v>
+        <v>1.4396</v>
       </c>
       <c r="E4" t="n">
-        <v>0.366</v>
+        <v>-0.1846</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3791</v>
+        <v>1.6242</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.0369</v>
+        <v>0.0959</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6228</v>
+        <v>-1.3767</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.4141</v>
+        <v>1.4726</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.9557</v>
+        <v>1.0935</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7086</v>
+        <v>-0.2513</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.6643</v>
+        <v>1.3447</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0812</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3314</v>
+        <v>-1.1254</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2502</v>
+        <v>0.1279</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3284</v>
+        <v>1.5523</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3284</v>
+        <v>2.5224</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9955000000000001</v>
+        <v>-0.2086</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8636</v>
+        <v>-0.3079</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1319</v>
+        <v>0.0993</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4582</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4582</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8263</v>
+        <v>1.0448</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2076</v>
+        <v>0.0927</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0339</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>1.5046</v>
@@ -844,13 +844,13 @@
         <v>2.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8306</v>
+        <v>-0.6121</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0779</v>
+        <v>-0.7776</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2472</v>
+        <v>0.1655</v>
       </c>
       <c r="V5" t="n">
         <v>-1.788</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8233</v>
+        <v>1.0324</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.196</v>
+        <v>-0.0959</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0194</v>
+        <v>1.1284</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1713</v>
@@ -922,13 +922,13 @@
         <v>1.1642</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1696</v>
+        <v>0.0395</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2423</v>
+        <v>-0.1422</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0727</v>
+        <v>0.1817</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GOMEZ SERRANO</t>
+          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7572</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7852</v>
+        <v>-1.1575</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5424</v>
+        <v>2.0884</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0959</v>
+        <v>-0.4603</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3767</v>
+        <v>0.0503</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4726</v>
+        <v>-0.5105</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0935</v>
+        <v>0.8324</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2513</v>
+        <v>1.4541</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3447</v>
+        <v>-0.6217</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-1.2927</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1254</v>
+        <v>-1.4039</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1279</v>
+        <v>0.1112</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5523</v>
+        <v>2.1344</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5224</v>
+        <v>3.1045</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.891</v>
+        <v>-0.5089</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9085</v>
+        <v>-1.0198</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0175</v>
+        <v>0.5109</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2343</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2343</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GIRALDO SISTIAGA</t>
+          <t>C. CUESTA DE SANTOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7411</v>
+        <v>0.8899</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2616</v>
+        <v>-0.4348</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0027</v>
+        <v>1.3246</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0484</v>
+        <v>-3.0369</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3098</v>
+        <v>-0.6228</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2614</v>
+        <v>-2.4141</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0412</v>
+        <v>-1.9557</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0412</v>
+        <v>0.7086</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-2.6643</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0896</v>
+        <v>-1.0812</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.351</v>
+        <v>-1.3314</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2614</v>
+        <v>0.2502</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3881</v>
+        <v>2.3284</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3881</v>
+        <v>2.3284</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0238</v>
+        <v>0.1402</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3028</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3266</v>
+        <v>0.0774</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3776</v>
+        <v>1.4582</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4582</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
+          <t>J. GIRALDO SISTIAGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5488</v>
+        <v>0.632</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4578</v>
+        <v>-0.2616</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0066</v>
+        <v>0.8937</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4603</v>
+        <v>-0.0484</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0503</v>
+        <v>-0.3098</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5105</v>
+        <v>0.2614</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8324</v>
+        <v>0.0412</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4541</v>
+        <v>0.0412</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6217</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2927</v>
+        <v>-0.0896</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4039</v>
+        <v>-0.351</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1112</v>
+        <v>0.2614</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1344</v>
+        <v>0.3881</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1045</v>
+        <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.891</v>
+        <v>-0.0852</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3201</v>
+        <v>-0.3028</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4291</v>
+        <v>0.2176</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2343</v>
+        <v>0.3776</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2343</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1348</v>
+        <v>0.2439</v>
       </c>
       <c r="E10" t="n">
         <v>1.1214</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9866</v>
+        <v>-0.8776</v>
       </c>
       <c r="G10" t="n">
         <v>0.0498</v>
@@ -1234,13 +1234,13 @@
         <v>0.3881</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3031</v>
+        <v>-0.194</v>
       </c>
       <c r="T10" t="n">
         <v>-0.2423</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0608</v>
+        <v>0.0482</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1304</v>
+        <v>-0.1032</v>
       </c>
       <c r="E11" t="n">
         <v>-0.0606</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0699</v>
+        <v>-0.0426</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>0.194</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0424</v>
+        <v>-0.0151</v>
       </c>
       <c r="T11" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2821</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3758</v>
+        <v>-1.4303</v>
       </c>
       <c r="E12" t="n">
         <v>-1.0913</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2845</v>
+        <v>-0.339</v>
       </c>
       <c r="G12" t="n">
         <v>-0.551</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1454</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>-0.1211</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2665</v>
+        <v>0.212</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8336</v>
+        <v>-4.3886</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7297</v>
+        <v>-3.2302</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1038</v>
+        <v>-1.1583</v>
       </c>
       <c r="G13" t="n">
         <v>-4.431</v>
@@ -1468,13 +1468,13 @@
         <v>1.3582</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8497</v>
+        <v>0.2947</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5473</v>
+        <v>0.0468</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3024</v>
+        <v>0.2479</v>
       </c>
       <c r="V13" t="n">
         <v>0.3299</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.5745</v>
+        <v>10.5744</v>
       </c>
       <c r="E14" t="n">
-        <v>4.878500000000001</v>
+        <v>4.878499999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>5.696</v>
+        <v>5.696099999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.585900000000001</v>
+        <v>-2.5859</v>
       </c>
       <c r="H14" t="n">
         <v>-2.0019</v>
@@ -1540,19 +1540,19 @@
         <v>13.5823</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.761499999999999</v>
+        <v>-7.7615</v>
       </c>
       <c r="R14" t="n">
         <v>21.3435</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.693700000000001</v>
+        <v>-1.6936</v>
       </c>
       <c r="T14" t="n">
         <v>-3.9875</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2937</v>
+        <v>2.2938</v>
       </c>
       <c r="V14" t="n">
         <v>1.2717</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.7969</v>
+        <v>7.9309</v>
       </c>
       <c r="E15" t="n">
-        <v>6.9042</v>
+        <v>7.2045</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8927</v>
+        <v>0.7264</v>
       </c>
       <c r="G15" t="n">
         <v>11.6434</v>
@@ -1624,13 +1624,13 @@
         <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0043</v>
+        <v>0.1383</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0173</v>
+        <v>-0.717</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0216</v>
+        <v>0.8552</v>
       </c>
       <c r="V15" t="n">
         <v>0.6119</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7548</v>
+        <v>3.2816</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6106</v>
+        <v>2.1101</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1443</v>
+        <v>1.1715</v>
       </c>
       <c r="G16" t="n">
         <v>0.5275</v>
@@ -1702,13 +1702,13 @@
         <v>0.7761</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4616</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6684</v>
+        <v>0.1679</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7932</v>
+        <v>0.8205</v>
       </c>
       <c r="V16" t="n">
         <v>0.9896</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3865</v>
+        <v>-1.1534</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2994</v>
+        <v>-1.9</v>
       </c>
       <c r="F17" t="n">
-        <v>0.913</v>
+        <v>0.7466</v>
       </c>
       <c r="G17" t="n">
         <v>2.9544</v>
@@ -1780,13 +1780,13 @@
         <v>0.9702</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3995</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6808</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7188</v>
+        <v>0.5524</v>
       </c>
       <c r="V17" t="n">
         <v>1.0806</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4943</v>
+        <v>-1.7124</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-0.4378</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6561</v>
+        <v>-1.2746</v>
       </c>
       <c r="G18" t="n">
         <v>-2.6872</v>
@@ -1858,13 +1858,13 @@
         <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0309</v>
+        <v>-0.249</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6539</v>
+        <v>-0.2535</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3771</v>
+        <v>0.0045</v>
       </c>
       <c r="V18" t="n">
         <v>1.2239</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8923</v>
+        <v>-2.7833</v>
       </c>
       <c r="E19" t="n">
         <v>-2.4616</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4307</v>
+        <v>-0.3217</v>
       </c>
       <c r="G19" t="n">
         <v>-2.0761</v>
@@ -1936,13 +1936,13 @@
         <v>0.7761</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3401</v>
+        <v>-0.231</v>
       </c>
       <c r="T19" t="n">
         <v>-0.4845</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1445</v>
+        <v>0.2535</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2821</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6987</v>
+        <v>-3.3199</v>
       </c>
       <c r="E20" t="n">
         <v>-3.607</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0917</v>
+        <v>0.287</v>
       </c>
       <c r="G20" t="n">
         <v>-2.3952</v>
@@ -2014,13 +2014,13 @@
         <v>0.5821</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0547</v>
+        <v>0.4335</v>
       </c>
       <c r="T20" t="n">
         <v>0.2557</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.201</v>
+        <v>0.1778</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. APARICIO IZQUIERDO</t>
+          <t>E. GARCÍA PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8402</v>
+        <v>-4.0229</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9414</v>
+        <v>-0.7614</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8988</v>
+        <v>-3.2616</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7725</v>
+        <v>-0.8204</v>
       </c>
       <c r="H21" t="n">
-        <v>0.234</v>
+        <v>-0.351</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0065</v>
+        <v>-0.4694</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1177</v>
+        <v>0.4931</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7219</v>
+        <v>0.4119</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.8396</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6548</v>
+        <v>-1.3135</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4879</v>
+        <v>-0.7629</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1669</v>
+        <v>-0.5506</v>
       </c>
       <c r="P21" t="n">
+        <v>-0.5821</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-1.9403</v>
-      </c>
       <c r="R21" t="n">
-        <v>0.9702</v>
+        <v>0.3881</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1741</v>
+        <v>0.1093</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8356</v>
+        <v>-0.2843</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0097</v>
+        <v>0.3937</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2716</v>
+        <v>-2.7298</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0478</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2239</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. GARCÍA PEREZ</t>
+          <t>A. APARICIO IZQUIERDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2776</v>
+        <v>-4.0244</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9616</v>
+        <v>-2.7412</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3161</v>
+        <v>-1.2832</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8204</v>
+        <v>-1.7725</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.351</v>
+        <v>0.234</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4694</v>
+        <v>-2.0065</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4931</v>
+        <v>-0.1177</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4119</v>
+        <v>1.7219</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08119999999999999</v>
+        <v>-1.8396</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3135</v>
+        <v>-1.6548</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7629</v>
+        <v>-1.4879</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5506</v>
+        <v>-0.1669</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5821</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3881</v>
+        <v>0.9702</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1454</v>
+        <v>-0.0101</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4845</v>
+        <v>-0.6354</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3392</v>
+        <v>0.6253</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.7298</v>
+        <v>-1.2716</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.0478</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.7298</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5366</v>
+        <v>-4.1034</v>
       </c>
       <c r="E23" t="n">
         <v>-3.1017</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4349</v>
+        <v>-1.0016</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7882</v>
@@ -2248,13 +2248,13 @@
         <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1157</v>
+        <v>0.549</v>
       </c>
       <c r="T23" t="n">
         <v>-0.4229</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5386</v>
+        <v>0.9719</v>
       </c>
       <c r="V23" t="n">
         <v>-0.894</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.5745</v>
+        <v>-9.9072</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.696099999999998</v>
+        <v>-5.6961</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.8783</v>
+        <v>-4.211200000000001</v>
       </c>
       <c r="G24" t="n">
         <v>2.585700000000001</v>
@@ -2326,13 +2326,13 @@
         <v>7.7614</v>
       </c>
       <c r="S24" t="n">
-        <v>1.6935</v>
+        <v>2.361</v>
       </c>
       <c r="T24" t="n">
         <v>-2.2938</v>
       </c>
       <c r="U24" t="n">
-        <v>3.9875</v>
+        <v>4.6548</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2715</v>
